--- a/Result/profitability/1906.xlsx
+++ b/Result/profitability/1906.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>1.387778780781446e-17</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>8.66625</v>
+        <v>8.907500000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05125000000000002</v>
+        <v>0.04875000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>8.418750000000001</v>
+        <v>9.03875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05125000000000002</v>
+        <v>0.08375000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>8.62125</v>
+        <v>9.0525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05125000000000002</v>
+        <v>0.12875</v>
       </c>
       <c r="N5" t="n">
-        <v>8.630000000000001</v>
+        <v>8.981249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08500000000000002</v>
+        <v>0.08750000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>8.92625</v>
+        <v>9.36125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06000000000000002</v>
+        <v>0.07125000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>8.9925</v>
+        <v>8.824999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03875000000000001</v>
+        <v>0.07375000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>8.56875</v>
+        <v>8.98875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>0.39</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09125000000000001</v>
+        <v>0.09125000000000003</v>
       </c>
       <c r="N9" t="n">
-        <v>8.905000000000001</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.08125000000000002</v>
       </c>
       <c r="N10" t="n">
-        <v>9.571250000000001</v>
+        <v>9.571249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.06000000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>9.934999999999999</v>
+        <v>9.935</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>0.05250000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>9.713749999999999</v>
+        <v>9.713750000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>757</v>
+      </c>
+      <c r="D75" t="n">
+        <v>671</v>
+      </c>
+      <c r="E75" t="n">
+        <v>86</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>27</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>37</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.03875000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.03875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-9.333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.359999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4194756554307115</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.675675675675676</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.809999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3282710280373831</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
